--- a/TEMPLATE_KPI.xlsx
+++ b/TEMPLATE_KPI.xlsx
@@ -221,6 +221,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000;[Red]0.000"/>
+  </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -550,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -596,14 +599,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,6 +611,14 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1006,52 +1010,52 @@
       <c r="H3" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="23" t="s">
         <v>20</v>
       </c>
       <c r="L3" s="14"/>
     </row>
     <row r="4" spans="1:12" ht="57" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="19" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="21"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="26"/>
     </row>
     <row r="5" spans="1:12" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="26"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/TEMPLATE_KPI.xlsx
+++ b/TEMPLATE_KPI.xlsx
@@ -222,9 +222,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000;[Red]0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,66 +558,66 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -923,7 +923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -933,105 +933,107 @@
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="11" width="22" customWidth="1"/>
+    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="35.1" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:12" ht="35.1" customHeight="1" thickTop="1">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="60" customHeight="1" thickBot="1">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="60" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:12" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="18" t="s">
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="14"/>
-    </row>
-    <row r="4" spans="1:12" ht="57" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="20" t="s">
+      <c r="L3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" ht="57" customHeight="1" thickTop="1">
+      <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
       <c r="I4" s="24" t="s">
         <v>21</v>
       </c>
@@ -1039,17 +1041,17 @@
       <c r="K4" s="25"/>
       <c r="L4" s="26"/>
     </row>
-    <row r="5" spans="1:12" ht="62.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:12" ht="62.25" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
       <c r="I5" s="27" t="s">
         <v>21</v>
       </c>
@@ -1057,7 +1059,7 @@
       <c r="K5" s="26"/>
       <c r="L5" s="26"/>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:12" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:H4"/>
@@ -1074,22 +1076,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="55" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -1100,7 +1102,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1111,7 +1113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -1122,7 +1124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1133,7 +1135,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
@@ -1144,7 +1146,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
@@ -1155,7 +1157,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>19</v>
       </c>
@@ -1166,7 +1168,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>20</v>
       </c>
@@ -1177,7 +1179,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>21</v>
       </c>
@@ -1188,15 +1190,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="20.100000000000001" customHeight="1"/>
+    <row r="13" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -1207,7 +1209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1218,7 +1220,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -1229,7 +1231,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A17" t="s">
         <v>52</v>
       </c>
@@ -1240,7 +1242,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1251,7 +1253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="20.100000000000001" customHeight="1">
       <c r="A19" t="s">
         <v>58</v>
       </c>
